--- a/evidence/pg16_race_sample_1.xlsx
+++ b/evidence/pg16_race_sample_1.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>b785987f0ea8da7f3c8c871d0fe49dd5</t>
+    <t>fa97c24a7f6f2b507e77f3cd0c100ec8</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>047d198c28e2f4ad654762c3f94a1aa3</t>
+    <t>2635f47c7623930aa5264b22631e78ef</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T06:12:02Z</t>
+    <t>2026-10-26T06:23:47Z</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/pg16_race_sample_1.xlsx
+++ b/evidence/pg16_race_sample_1.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>00202da61772061a2371df797b963f4b</t>
+    <t>3834dabe264e406fa0303ea7f2fd704f</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>42f7c3164d8cb976800fd3cf3cbf40bf</t>
+    <t>544d222a91f0d9f4a0c9f1d6f32b5105</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T07:05:23Z</t>
+    <t>2026-10-26T07:29:25Z</t>
   </si>
   <si>
     <t>precision</t>
